--- a/AAII_Financials/Quarterly/CTAS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTAS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>CTAS</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45808</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45351</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45260</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45169</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45077</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44895</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44804</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44712</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44620</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44530</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44439</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44347</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44165</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44074</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43982</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43890</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43799</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43708</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43616</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43524</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43434</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43343</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43159</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43069</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42978</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42886</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42794</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42704</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2905200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2841400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2800000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2718100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2667700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2609200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2561800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2501600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2470900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2406200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2377200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2342300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2284500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2190000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4341300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2166500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2074700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1960500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3819200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1897000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1835700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1777100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3503600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1746600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1619600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1810600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3654900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1811100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1793700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1682300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3416200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1698000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1669600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1589100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1606400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1611500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1530300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1255400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1271100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1266700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1424900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1393000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1387500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1351600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1341700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1289800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1285100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1249500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1255500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1218300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1235600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1200800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1195700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1156000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2290800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1138300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1128500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1062400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2031300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>994200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>976600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>967500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1857500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>920400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>911800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>986300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1953400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>962000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>970200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>927200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1866400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>923300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>917200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>888700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>890100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>872200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>851600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>695400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>705900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>690200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1480300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1448500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1412500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1366600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1326000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1319300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1276700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1252100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1215400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1187800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1141500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1141600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1088800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2050500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1028200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>946200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>898100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1787900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>902800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>859100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>809600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1646100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>826200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>707800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>824300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1701500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>849100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>823500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>755100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1549800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>774700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>752400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>700400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>716300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>739400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>678700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>560000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>565200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,13 +1248,14 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>34100</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1249,11 +1263,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>30800</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1261,11 +1275,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>26600</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1273,11 +1287,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3">
         <v>24500</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,13 +1496,16 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>16100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1505,11 +1525,11 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>15000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1541,11 +1561,11 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>5100</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1553,12 +1573,12 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>33700</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1566,93 +1586,96 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>12700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>9800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>13100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>4000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>63700</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>9300</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>3300</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E15" s="3">
         <v>102200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>99700</v>
       </c>
-      <c r="G15" s="3">
-        <v>64800</v>
-      </c>
       <c r="H15" s="3">
+        <v>69400</v>
+      </c>
+      <c r="I15" s="3">
         <v>98100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>95100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>94500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>76700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>85700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>84000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>82400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>55600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>78800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>73700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>36400</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
@@ -1666,8 +1689,8 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2217000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2181500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2144300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2070200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1999300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1970400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1940600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1908300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1885400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1877500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1841800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1813700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1743200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3456300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1726300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1670300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1552900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3043900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1502800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1479200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1450600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2801000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1396900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1412200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1496000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3014300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1505000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1479300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1404100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2875400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1432700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1404100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1389100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1371200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1362400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1353000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1063400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1070600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1062700</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>688200</v>
+      </c>
+      <c r="E18" s="3">
         <v>659900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>655700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>617900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>597500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>609900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>591400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>561000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>562600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>520800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>499700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>500600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>470800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>446800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>885000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>440200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>404500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>407600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>775300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>394200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>356500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>326500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>702600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>349700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>207500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>314600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>640600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>306100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>314400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>278200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>540800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>265300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>265600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>200000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>235200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>249100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>177300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>192000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>200500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,11 +2130,11 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
@@ -2112,558 +2146,573 @@
         <v>100</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>200</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>400</v>
       </c>
       <c r="AC20" s="3">
         <v>400</v>
       </c>
       <c r="AD20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>70300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>400</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>300</v>
       </c>
       <c r="AL20" s="3">
         <v>300</v>
       </c>
       <c r="AM20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN20" s="3">
         <v>100</v>
       </c>
-      <c r="AN20" s="3">
-        <v>0</v>
-      </c>
       <c r="AO20" s="3">
         <v>0</v>
       </c>
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>758700</v>
+      </c>
+      <c r="E21" s="3">
         <v>762100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>756600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>717600</v>
       </c>
-      <c r="G21" s="3">
-        <v>662200</v>
-      </c>
       <c r="H21" s="3">
+        <v>666800</v>
+      </c>
+      <c r="I21" s="3">
         <v>708000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>686500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>655500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>639300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>606500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>583700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>583000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>526400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>525600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1086800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>540300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>506900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>508300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>972100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>492100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>454700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>423700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>895500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>445900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>304200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>411200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>827400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>398300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>408400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>370000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>785800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>352000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>340400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>266500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>305800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>317900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>242300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>236700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>244400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>247200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E22" s="3">
         <v>28200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>24200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>26700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>28800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>56600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>27700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>22000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>43800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21900</v>
-      </c>
-      <c r="W22" s="3">
-        <v>24600</v>
       </c>
       <c r="X22" s="3">
         <v>24600</v>
       </c>
       <c r="Y22" s="3">
+        <v>24600</v>
+      </c>
+      <c r="Z22" s="3">
         <v>49100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>24600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>26000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>53500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>27300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>26800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>49200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>25900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>29100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>30300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>45400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>13700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>13300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>648400</v>
+      </c>
+      <c r="E23" s="3">
         <v>632500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>628500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>595900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>575400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>586400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>565700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>536700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>527100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>496200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>473900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>476400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>445900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>418400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>828900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>412600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>381500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>385600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>731700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>372300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>332000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>302000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>653800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>325200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>181700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>289100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>587600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>279000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>288900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>251600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>561900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>241400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>241000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>174500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>206400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>219100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>132000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>178300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>187200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>189800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>137400</v>
+      </c>
+      <c r="E24" s="3">
         <v>130000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>133200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>104800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>127200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>122900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>117200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>84600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>112800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>98600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>99200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>91300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>99700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>92500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>152900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>60900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>87000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>70200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>105800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>41100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>64300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>43600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>68900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>25200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>37100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>54500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>90300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>28200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>61500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>50600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>106400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>25600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>62700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>29200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>68600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>58000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>49900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>61400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>65300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E26" s="3">
         <v>502500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>495300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>491100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>448300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>463500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>448500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>452000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>414300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>397600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>374600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>385100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>346200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>325800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>676000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>351700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>294500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>315400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>625800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>331200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>267700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>258400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>584900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>300000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>144600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>234500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>497300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>250800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>227400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>200900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>455500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>215800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>178400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>145300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>137700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>161100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>82200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>117000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>122000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>136200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>509400</v>
+      </c>
+      <c r="E27" s="3">
         <v>500900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>493700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>489500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>446700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>461900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>446900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>450400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>412900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>396000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>373200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>383500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>344900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>324500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>673200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>350200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>293000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>313900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>622700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>329500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>266000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>256500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>580800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>297900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>143300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>232300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>492600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>248300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>226800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>198100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>449400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>212900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>177100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>140000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>135600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>157900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>81400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>114400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>120000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>133400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3231,49 +3292,52 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-300</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>2400</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>156800</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-600</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>56100</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>2100</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>1100</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>35400</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,11 +3630,11 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
@@ -3576,192 +3646,198 @@
         <v>-100</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-400</v>
       </c>
       <c r="AC32" s="3">
         <v>-400</v>
       </c>
       <c r="AD32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-70300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>-300</v>
       </c>
       <c r="AL32" s="3">
         <v>-300</v>
       </c>
       <c r="AM32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AN32" s="3">
         <v>-100</v>
       </c>
-      <c r="AN32" s="3">
-        <v>0</v>
-      </c>
       <c r="AO32" s="3">
         <v>0</v>
       </c>
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E33" s="3">
         <v>502500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>495300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>491100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>448300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>463500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>448500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>452000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>414300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>397600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>374600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>385100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>346200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>325800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>673200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>350200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>293000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>313900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>622700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>329500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>266000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>256500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>580800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>297900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>143300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>232300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>492300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>248300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>225500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>200600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>449300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>209600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>184900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>296800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>135000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>214000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>83400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>115400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>155400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>135200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E35" s="3">
         <v>502500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>495300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>491100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>448300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>463500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>448500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>452000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>414300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>397600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>374600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>385100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>346200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>325800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>673200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>350200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>293000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>313900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>622700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>329500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>266000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>256500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>580800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>297900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>143300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>232300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>492300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>248300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>225500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>200600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>449300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>209600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>184900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>296800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>135000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>214000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>83400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>115400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>155400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>135200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45808</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45351</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45260</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45169</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45077</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44895</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44804</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44712</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44620</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44530</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44439</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44347</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44165</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44074</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43982</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43890</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43799</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43708</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43616</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43524</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43434</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43343</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43159</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43069</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42978</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42886</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42794</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42704</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>289000</v>
+      </c>
+      <c r="E41" s="3">
         <v>183200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>138100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>264000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>243400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>101400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>342000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>128500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>85600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>88100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>124100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>88600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>89800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>74600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>90500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>84100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>113200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>79700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>493600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>553600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>703200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>421500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>145400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>234400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>226500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>102100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>96600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>80900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>88500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>118400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>138700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>152600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>236000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>191400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>169300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>147200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>143600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4443,882 +4533,906 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
         <v>33700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>22700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>21600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>22200</v>
       </c>
-      <c r="AN42" s="3">
-        <v>0</v>
-      </c>
       <c r="AO42" s="3">
         <v>0</v>
       </c>
       <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1555200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1543000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1484300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1421000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1417400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1398500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1381400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1293800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1244200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1262100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1274000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1197300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1153000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1136100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1149500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1082800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1027900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1070700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1064600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>938600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>924000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>987400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>967100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>866400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>870400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>966300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>974000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>917500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>917600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>920600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>940700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>845100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>824200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>800900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>799300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>731600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>780300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>619400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>608700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>586400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1722600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1691100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1661100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1622100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1584800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1520900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1488600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1460100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1450300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1476800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1510600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1519900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1518500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1530300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>514800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>473900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>472200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>486800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>464900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>463700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>481800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>533200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>534100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>488200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>408900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>352900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>348300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>336300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>334600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>339800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>321900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>303800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>280300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>274800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>272800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>283200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>278200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>272200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>263300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>262200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E45" s="3">
         <v>96100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>96600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>96500</v>
       </c>
       <c r="G45" s="3">
         <v>96500</v>
       </c>
       <c r="H45" s="3">
+        <v>96500</v>
+      </c>
+      <c r="I45" s="3">
         <v>94800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>95000</v>
       </c>
       <c r="J45" s="3">
         <v>95000</v>
       </c>
       <c r="K45" s="3">
+        <v>95000</v>
+      </c>
+      <c r="L45" s="3">
         <v>94600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>94300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>93900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>94100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>92500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>90400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1139000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1116600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1041400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1045200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1012900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>995600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>943900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>904300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>898400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>890100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>885000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>944000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>941400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>933900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>887500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>882500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>864900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>837200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>734600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>717600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>712600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>696700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>704400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>591100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>585100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>582500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3853000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3602900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3540100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3375900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3436200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3341400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3170400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3043400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3185200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3031000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3036700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2987500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2938500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2910200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2893200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2747800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2632000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2686700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2655500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2477700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2843300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2978600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3102800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2666200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2309700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2497700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2490300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2289800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2236300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2223800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2215900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2104400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1977900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1979600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2043400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1924600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1954500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1629900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1600700</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1594700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>438700</v>
+      </c>
+      <c r="E47" s="3">
         <v>407100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>386300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>369500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>339500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>336900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>340100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>325700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>302200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>294300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>270000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>266900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>247200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>243600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>239300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>242900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>259900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>289100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>295300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>274600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>264600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>252500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>240400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>214800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>212800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>218900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>209000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>192300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>191800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>183500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>180300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>175600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>178500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>175700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>163600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>164800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>148200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>140500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>140900</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1916400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1972200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1957000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1921100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1757300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1819800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1774800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1745600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1615300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1692300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1643000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1620900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1468400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1536700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1516900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1503800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1493700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1480200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1455100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1460500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1487000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1486800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1498400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1537500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1563000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1600000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1594800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1585400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1430700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1424100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1410500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1394600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1382700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1367600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1353200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1340700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1323500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1090200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1067200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1033200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4016300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3955000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3958600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3888100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4017000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3842900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3812300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3688200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3803600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3700500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3605500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3589200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3640200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3407200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3529200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3530900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3546500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3509100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3388800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3397100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3404800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3388200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3369200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3369300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3355200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3370200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3367300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3365600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3577400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3594000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3595100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3385900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3422000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3402900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3406500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3422800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3401300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1402800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1406200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1398400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,8 +5678,11 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5602,65 +5722,65 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
         <v>358900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>244100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>239200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>232200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>232700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>228900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>227200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>227100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>229300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>232000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>230000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>227100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>221300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>216100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>212000</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-      <c r="AG52" s="3" t="s">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>222000</v>
-      </c>
-      <c r="AI52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>8</v>
@@ -5671,8 +5791,8 @@
       <c r="AL52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM52" s="3">
-        <v>0</v>
+      <c r="AM52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AN52" s="3">
         <v>0</v>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10529100</v>
+      </c>
+      <c r="E54" s="3">
         <v>10233700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10132900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9837700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9825200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9611100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9366500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9068700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9168800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8978900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8813900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8719700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8546400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8466000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8427000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8261000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8147300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8168600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8017400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7857800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8236800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8347500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8454800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8043400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7669900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7902000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7887300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7661900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7436700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7433700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7405100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7287200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6958200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6928600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6978800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6851600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>6844100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4271200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>4214600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>4167100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>461200</v>
+      </c>
+      <c r="E57" s="3">
         <v>481000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>503300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>462300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>485100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>408500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>418300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>395900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>339200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>307900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>316700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>314700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>302300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>281600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>311000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>292300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>251500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>235100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>240300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>203000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>230800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>237900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>274000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>252500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>231000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>243200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>254600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>237200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>226000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>214600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>211900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>214000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>215100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>172200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>163000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>189600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>177100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>127900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>127800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1055500</v>
+      </c>
+      <c r="E58" s="3">
         <v>283600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>603500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>51700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>50700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>498700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>677700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>662200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>495300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>44400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>254100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>43800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>43700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>292000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>435400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>507500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>311600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1509100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1116500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1275200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>899100</v>
-      </c>
-      <c r="X58" s="3">
-        <v>249900</v>
       </c>
       <c r="Y58" s="3">
         <v>249900</v>
       </c>
       <c r="Z58" s="3">
+        <v>249900</v>
+      </c>
+      <c r="AA58" s="3">
         <v>249800</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
-        <v>199800</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>199800</v>
       </c>
       <c r="AD58" s="3">
+        <v>199800</v>
+      </c>
+      <c r="AE58" s="3">
         <v>338800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>312300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>217500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>173500</v>
       </c>
-      <c r="AH58" s="3" t="s">
+      <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
         <v>187500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>300000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>307500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>362900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>399400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>66000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>230400</v>
+      </c>
+      <c r="E59" s="3">
         <v>191800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>184400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>261300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>217300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>203100</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>84600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>201200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>101000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>157000</v>
       </c>
-      <c r="P59" s="3" t="s">
+      <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>807300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>799800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>869800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>879400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>821100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>790900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>804200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>782600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>984600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>591000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>654200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>623600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>842900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>546900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>589400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>562300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>729300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>465100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>560800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>557900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>691400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>547800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>590900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>416700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>554900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>417400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2687000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1816900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2076000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1507800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1644500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1941100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2007800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1984900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1828500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1273900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1357600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1168800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1230100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1388300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1553700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1599500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1432900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2623500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2177900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2269000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1934100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1270400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1508500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1093400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>885200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1066600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1297300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1122900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1127700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>994400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1114700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>679100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>775900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>917600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1154400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1044800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1130900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>944000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>748800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>710900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1650500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2634600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2633600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2623600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2603700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2193100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2168900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2175800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2172800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2621000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2613200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2618600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2624700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2625100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2485300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2484600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2483900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1343500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1343400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1343200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1642800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2291400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2290900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2290400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2539700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2539200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2538600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2538100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2537500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2537000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2536400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2535900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2535300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2534800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2534200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2533700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2770600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>745200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1044800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1044600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>508900</v>
+      </c>
+      <c r="E62" s="3">
         <v>486300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>472600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>466200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>409600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>417800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>419800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>412100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>359700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>368800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>351400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>354700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>311600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>322600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>957500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>947300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>922200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>907700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>933000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>936300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>972100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>969200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1057400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1054800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1009800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>971900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>946500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>950300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>768700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>722900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>726700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>726300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>630500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>582300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>737200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>707300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>639800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>403700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>395300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>424300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5389300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5445300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5677500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5082000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5140800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5018900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5073400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5047300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4852400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4744800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4819400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4642000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4682400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4832700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4996500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5031400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4839100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4874700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4454300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4548500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4549000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4531000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4856800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4438600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4434700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4577700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4782400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4611200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4433900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4254200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4377800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3941200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3941700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4034600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4425800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4285700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4541300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2092900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2188900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2179700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13074000</v>
+      </c>
+      <c r="E72" s="3">
         <v>12743700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12421900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12107300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11798500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11507800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11202500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10912000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10618000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10341200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10081300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9844100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9597300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9368700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9160300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8953400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8719200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8522300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8305100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8109400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7877000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7688400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7509500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7596500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7296500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7151800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6917300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6939200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6691200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6465100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6261800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6239500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5837800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5651700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5349500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5388000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5170800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5086600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4968400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4970600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5139900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4788400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4455300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4755700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4684500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4592200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4293100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4021400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4316400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4234100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3994500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4077600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3864000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3633300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3430500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3229600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3308200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3293900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3563100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3309200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3687800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3816500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3598000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3604800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3235200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3324300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3105000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3050700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3002700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3179500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3027200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3346000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3016500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2894000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2553000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2565900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2302800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2178300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2025700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1987400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45808</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45351</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45260</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45169</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45077</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44895</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44804</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44712</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44620</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44530</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44439</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44347</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44165</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44074</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43982</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43890</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43799</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43708</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43616</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43524</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43434</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43343</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43159</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43069</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42978</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42886</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42794</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42704</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E81" s="3">
         <v>502500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>495300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>491100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>448300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>463500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>448500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>452000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>414300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>397600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>374600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>385100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>346200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>325800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>673200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>350200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>293000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>313900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>622700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>329500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>266000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>256500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>580800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>297900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>143300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>232300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>492300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>248300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>225500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>200600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>449300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>209600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>184900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>296800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>135000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>214000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>83400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>115400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>155400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>135200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E83" s="3">
         <v>76400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>75500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>73800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>70800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>69200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>67600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>64200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>63500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>63100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>41400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>62200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>201300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>100000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>102400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>196600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>97900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>98100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>97200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>192700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>96200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>96600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>96200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>186300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>92000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>93800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>91700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>174700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>86300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>74500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>66100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>70300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>68500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>64900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>44700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>43900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>43200</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>709100</v>
+      </c>
+      <c r="E89" s="3">
         <v>621500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>531200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>414500</v>
       </c>
-      <c r="G89" s="3">
-        <v>635700</v>
-      </c>
       <c r="H89" s="3">
+        <v>640300</v>
+      </c>
+      <c r="I89" s="3">
         <v>620500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>444700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>460400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>681800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>657100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>392700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>336900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>553600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>425000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>619100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>298200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>550600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>393300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>593800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>262100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>455900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>331900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>573000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>312300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>356900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>363200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>571400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>276900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>397100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>326200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>344600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>163000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>303300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>281900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>124600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>254400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>280100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>182000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>144100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-90900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-106300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-102000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-114600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-99900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-101400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-92900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-101900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-107000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-93800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-106700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-107000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-77700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-76400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-70000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-74800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-57200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-59900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-48700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-43100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-42800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-57700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-40900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-63200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-126200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-64700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-68900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-70200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-137600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-64500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-75700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-63600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-69900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-62500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-54700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-63400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-76600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-78600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-158300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-101100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-192900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-116200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-149300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-125400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-239500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-109500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-221100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-112400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-169800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-120100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-97200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-171400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-86600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-86300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-164700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-151600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-84300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-48600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-51200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-48900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-104800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-131700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-78100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-72600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-86600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-70800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-45700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-83800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-78800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>72600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-73400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>8600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-100600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,74 +10455,75 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>180600</v>
+      </c>
+      <c r="E96" s="3">
         <v>180700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>182300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>157800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>157900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>158100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>157300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>138200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>137600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>137500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>138300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>117600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>117500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>117400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-215000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-97700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-98200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-99000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-177900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-79100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-79500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -10297,11 +10531,11 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>100</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-443100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-540000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-275000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-424000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-468400</v>
-      </c>
       <c r="H100" s="3">
+        <v>-473000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-372100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-182600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-591300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-368000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-393700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-283400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-202400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-398200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-328200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-446400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-226200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-459400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-258700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-819900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-590100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-469800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-444600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>34500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-394900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-250300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-310000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-193600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-308000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-257900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-307400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-112500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-271900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-282800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-311400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1886100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-104600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-106000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-97000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>6600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>105800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>62700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-125800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>121000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>21000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-240600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>213500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>42900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-36000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>35600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-29000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-380500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-413900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-60000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-149600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>557800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>276100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-89000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>7900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>129900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>15800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-50200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-13800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-83400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>44600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>22100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>22000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>3700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>44400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-40100</v>
       </c>
     </row>
